--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45081-2022 artfynd.xlsx
+++ b/artfynd/A 45081-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136059252</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
